--- a/ResourcesBD/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesBD/ExcelTemplateForOutletCreation.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Excel Template" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" concurrentManualCount="8"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="135">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -294,649 +294,136 @@
     <t>CA101</t>
   </si>
   <si>
+    <t>CA1299</t>
+  </si>
+  <si>
+    <t>CA405</t>
+  </si>
+  <si>
+    <t>CA703</t>
+  </si>
+  <si>
+    <t>ABCD</t>
+  </si>
+  <si>
+    <t>03001</t>
+  </si>
+  <si>
+    <t>BDEBCHT018</t>
+  </si>
+  <si>
+    <t>0345224422</t>
+  </si>
+  <si>
+    <t>Hammad Outlet17</t>
+  </si>
+  <si>
+    <t>Hammad Outlet18</t>
+  </si>
+  <si>
+    <t>Hammad Outlet19</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL65444</t>
+  </si>
+  <si>
+    <t>03409419300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC0EFD</t>
+  </si>
+  <si>
+    <t>03410887200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLEA06B</t>
+  </si>
+  <si>
+    <t>03411859600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLABA79</t>
+  </si>
+  <si>
+    <t>03414399000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00001 </t>
+  </si>
+  <si>
     <t>00001</t>
   </si>
   <si>
-    <t>CA1299</t>
-  </si>
-  <si>
-    <t>CA405</t>
-  </si>
-  <si>
-    <t>CA703</t>
-  </si>
-  <si>
-    <t>ABCD</t>
-  </si>
-  <si>
-    <t>03001</t>
-  </si>
-  <si>
-    <t>BDEBCHT018</t>
-  </si>
-  <si>
-    <t>0325699999331</t>
-  </si>
-  <si>
-    <t>0345224422</t>
-  </si>
-  <si>
-    <t>Hammad Outlet17</t>
-  </si>
-  <si>
-    <t>0325699999332</t>
-  </si>
-  <si>
-    <t>Hammad Outlet18</t>
-  </si>
-  <si>
-    <t>0325699999333</t>
-  </si>
-  <si>
-    <t>Hammad Outlet19</t>
-  </si>
-  <si>
-    <t>0325699999334</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL4040F</t>
-  </si>
-  <si>
-    <t>03499353300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL03F22</t>
-  </si>
-  <si>
-    <t>03502920500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL505CD</t>
-  </si>
-  <si>
-    <t>03507810800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL7C978</t>
-  </si>
-  <si>
-    <t>03511424400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL67F0E</t>
-  </si>
-  <si>
-    <t>03102302500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL27750</t>
-  </si>
-  <si>
-    <t>03105367800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLBF00F</t>
-  </si>
-  <si>
-    <t>03108044100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLB8856</t>
-  </si>
-  <si>
-    <t>03110525600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL5B2EE</t>
-  </si>
-  <si>
-    <t>03166841100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD065F</t>
-  </si>
-  <si>
-    <t>03170275500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL14410</t>
-  </si>
-  <si>
-    <t>03171970800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL44454</t>
-  </si>
-  <si>
-    <t>03174406200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL43F34</t>
-  </si>
-  <si>
-    <t>03006356800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL67B28</t>
-  </si>
-  <si>
-    <t>03008672400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL41F05</t>
-  </si>
-  <si>
-    <t>03010595000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL98753</t>
-  </si>
-  <si>
-    <t>03012500700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL16ABF</t>
-  </si>
-  <si>
-    <t>03633940500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL46937</t>
-  </si>
-  <si>
-    <t>03634523900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE5010</t>
-  </si>
-  <si>
-    <t>03635066100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL1DE90</t>
-  </si>
-  <si>
-    <t>03635601600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL625B6</t>
-  </si>
-  <si>
-    <t>03178107400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLFDE2B</t>
-  </si>
-  <si>
-    <t>03178453000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD893B</t>
-  </si>
-  <si>
-    <t>03178727700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF2056</t>
-  </si>
-  <si>
-    <t>03179003400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3147A</t>
-  </si>
-  <si>
-    <t>03085371600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC3D7E</t>
-  </si>
-  <si>
-    <t>03088938600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL77BEE</t>
-  </si>
-  <si>
-    <t>03091673900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLEBC9A</t>
-  </si>
-  <si>
-    <t>03093389000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL0AF59</t>
-  </si>
-  <si>
-    <t>03802438200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLAE8A3</t>
-  </si>
-  <si>
-    <t>03805274300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE2278</t>
-  </si>
-  <si>
-    <t>03807092400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLB3BDD</t>
-  </si>
-  <si>
-    <t>03808201800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLCA416</t>
-  </si>
-  <si>
-    <t>03414321900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL349F9</t>
-  </si>
-  <si>
-    <t>03415437900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL269AB</t>
-  </si>
-  <si>
-    <t>03416561500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF91F9</t>
-  </si>
-  <si>
-    <t>03417367200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD9A39</t>
-  </si>
-  <si>
-    <t>03667266700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLACC4E</t>
-  </si>
-  <si>
-    <t>03669129700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLAF0F9</t>
-  </si>
-  <si>
-    <t>03670893500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF15EA</t>
-  </si>
-  <si>
-    <t>03673304700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL9F33B</t>
-  </si>
-  <si>
-    <t>03585120100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL1CC9D</t>
-  </si>
-  <si>
-    <t>03587950000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD1BA9</t>
-  </si>
-  <si>
-    <t>03590287700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL45CEC</t>
-  </si>
-  <si>
-    <t>03592737900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLCE5B6</t>
-  </si>
-  <si>
-    <t>03557204500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL135E7</t>
-  </si>
-  <si>
-    <t>03558212300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLFAD5D</t>
-  </si>
-  <si>
-    <t>03558971500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLB1F1F</t>
-  </si>
-  <si>
-    <t>03559875900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLBFFA2</t>
-  </si>
-  <si>
-    <t>03567797200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLEA6DB</t>
-  </si>
-  <si>
-    <t>03568262900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLAE8B4</t>
-  </si>
-  <si>
-    <t>03568764900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL60760</t>
-  </si>
-  <si>
-    <t>03569263400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL32ED6</t>
-  </si>
-  <si>
-    <t>03126487800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL66635</t>
-  </si>
-  <si>
-    <t>03126935300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLEF711</t>
-  </si>
-  <si>
-    <t>03127254400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL6EC3A</t>
-  </si>
-  <si>
-    <t>03127554200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL252F7</t>
-  </si>
-  <si>
-    <t>03819696000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLDC275</t>
-  </si>
-  <si>
-    <t>03820609800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLFD220</t>
-  </si>
-  <si>
-    <t>03821273800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC231E</t>
-  </si>
-  <si>
-    <t>03821984200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL4A5DD</t>
-  </si>
-  <si>
-    <t>03786179600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL98CFE</t>
-  </si>
-  <si>
-    <t>03788800200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD2D57</t>
-  </si>
-  <si>
-    <t>03790291200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL70C1A</t>
-  </si>
-  <si>
-    <t>03792304800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL60E8A</t>
-  </si>
-  <si>
-    <t>03728970300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL6F33B</t>
-  </si>
-  <si>
-    <t>03730836700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLAFF04</t>
-  </si>
-  <si>
-    <t>03732191300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL87BCC</t>
-  </si>
-  <si>
-    <t>03733573000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLA8FDE</t>
-  </si>
-  <si>
-    <t>03473844100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD9A68</t>
-  </si>
-  <si>
-    <t>03476279800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL563B3</t>
-  </si>
-  <si>
-    <t>03477878400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLDBD4D</t>
-  </si>
-  <si>
-    <t>03479637100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3A0F7</t>
-  </si>
-  <si>
-    <t>03429125900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL1A63A</t>
-  </si>
-  <si>
-    <t>03432127700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLB9A43</t>
-  </si>
-  <si>
-    <t>03434418300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE665B</t>
-  </si>
-  <si>
-    <t>03436666100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2811B</t>
-  </si>
-  <si>
-    <t>03542097300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL46367</t>
-  </si>
-  <si>
-    <t>03546284400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL96E0D</t>
-  </si>
-  <si>
-    <t>03552103600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL74B6A</t>
-  </si>
-  <si>
-    <t>03555251600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF3AC9</t>
-  </si>
-  <si>
-    <t>03624801900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF2067</t>
-  </si>
-  <si>
-    <t>03629740700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLFE573</t>
-  </si>
-  <si>
-    <t>03633963100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLA3439</t>
-  </si>
-  <si>
-    <t>03636367900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC91F6</t>
-  </si>
-  <si>
-    <t>03973075200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLBB1CB</t>
-  </si>
-  <si>
-    <t>03977672400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF7C56</t>
-  </si>
-  <si>
-    <t>03981221300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL6E4FB</t>
-  </si>
-  <si>
-    <t>03986659700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL472F8</t>
-  </si>
-  <si>
-    <t>03510877200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE4C96</t>
-  </si>
-  <si>
-    <t>03511797300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2AD32</t>
-  </si>
-  <si>
-    <t>03512341800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL54603</t>
-  </si>
-  <si>
-    <t>03512894200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE62F5</t>
-  </si>
-  <si>
-    <t>03552159400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL299F5</t>
-  </si>
-  <si>
-    <t>03554882400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC1C58</t>
-  </si>
-  <si>
-    <t>03556444500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL62189</t>
-  </si>
-  <si>
-    <t>03557867300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL1330D</t>
-  </si>
-  <si>
-    <t>03747607400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL148D9</t>
-  </si>
-  <si>
-    <t>03748611200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE47A2</t>
-  </si>
-  <si>
-    <t>03749321800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLADEA2</t>
-  </si>
-  <si>
-    <t>03750050400</t>
+    <t>AUTO_OUTLD054F</t>
+  </si>
+  <si>
+    <t>03178270500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE2358</t>
+  </si>
+  <si>
+    <t>03179270600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5FD38</t>
+  </si>
+  <si>
+    <t>03180106700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC61CF</t>
+  </si>
+  <si>
+    <t>03180933600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1F7B8</t>
+  </si>
+  <si>
+    <t>03300124100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCC4FE</t>
+  </si>
+  <si>
+    <t>03301238800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF1F08</t>
+  </si>
+  <si>
+    <t>03302260600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLEE7E8</t>
+  </si>
+  <si>
+    <t>03303520000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0A15A</t>
+  </si>
+  <si>
+    <t>03223040600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE0108</t>
+  </si>
+  <si>
+    <t>03225272900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4B7D4</t>
+  </si>
+  <si>
+    <t>03226759800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL60D83</t>
+  </si>
+  <si>
+    <t>03228174400</t>
   </si>
 </sst>
 </file>
@@ -1572,7 +1059,7 @@
     </row>
     <row r="2" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>298</v>
+        <v>127</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>74</v>
@@ -1599,7 +1086,7 @@
         <v>26.36</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>24.570394270904828</v>
+        <v>24.01085412757735</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>80</v>
@@ -1646,61 +1133,61 @@
       <c r="AT2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AU2" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="AV2" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="AV2" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="AW2" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AZ2" s="1" t="s">
         <v>88</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="BC2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BD2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BE2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BF2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="BD2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BE2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF2" s="1" t="s">
+      <c r="BG2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="BG2" s="1" t="s">
+      <c r="BJ2" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="BJ2" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="BK2" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="BU2" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BV2" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>300</v>
+        <v>129</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>75</v>
@@ -1721,7 +1208,7 @@
         <v>26.36</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>24.02492776592052</v>
+        <v>24.139473632188565</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>80</v>
@@ -1768,61 +1255,61 @@
       <c r="AT3" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="AU3" s="1" t="s">
+      <c r="AU3" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="AV3" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="AV3" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="AW3" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AY3" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AZ3" s="1" t="s">
         <v>88</v>
       </c>
       <c r="BA3" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="BC3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BD3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BE3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BF3" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="BD3" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BE3" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF3" s="1" t="s">
+      <c r="BG3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="BG3" s="1" t="s">
+      <c r="BJ3" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="BK3" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="BJ3" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="BK3" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="BU3" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BV3" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>302</v>
+        <v>131</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>75</v>
@@ -1843,7 +1330,7 @@
         <v>26.36</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>24.935151686710018</v>
+        <v>24.77904887564629</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>80</v>
@@ -1890,61 +1377,61 @@
       <c r="AT4" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="AU4" s="1" t="s">
+      <c r="AU4" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AV4" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="AV4" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="AW4" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AY4" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AZ4" s="1" t="s">
         <v>88</v>
       </c>
       <c r="BA4" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="BC4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BD4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BE4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BF4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="BD4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BE4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF4" s="1" t="s">
+      <c r="BG4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="BG4" s="1" t="s">
+      <c r="BJ4" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="BK4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="BJ4" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="BK4" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="BU4" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BV4" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>304</v>
+        <v>133</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>75</v>
@@ -1965,7 +1452,7 @@
         <v>26.36</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>24.881525053126566</v>
+        <v>24.23184957564713</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>80</v>
@@ -2012,50 +1499,50 @@
       <c r="AT5" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="AU5" s="1" t="s">
+      <c r="AU5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AV5" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="AV5" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="AW5" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AY5" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AZ5" s="1" t="s">
         <v>88</v>
       </c>
       <c r="BA5" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="BC5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BD5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BE5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BF5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="BD5" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BE5" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF5" s="1" t="s">
+      <c r="BG5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="BG5" s="1" t="s">
+      <c r="BJ5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="BK5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="BJ5" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="BK5" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="BU5" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BV5" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/ResourcesBD/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesBD/ExcelTemplateForOutletCreation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="183">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -424,6 +424,150 @@
   </si>
   <si>
     <t>03228174400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL249EC</t>
+  </si>
+  <si>
+    <t>03539130700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA2B6E</t>
+  </si>
+  <si>
+    <t>03540558600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL7CE9F</t>
+  </si>
+  <si>
+    <t>03541597700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL59EC1</t>
+  </si>
+  <si>
+    <t>03542875200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA9C3D</t>
+  </si>
+  <si>
+    <t>03909766800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL96B93</t>
+  </si>
+  <si>
+    <t>03911744600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4E430</t>
+  </si>
+  <si>
+    <t>03913291900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB6B16</t>
+  </si>
+  <si>
+    <t>03915102400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3DE0B</t>
+  </si>
+  <si>
+    <t>03662644600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5C07A</t>
+  </si>
+  <si>
+    <t>03664407300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL25C26</t>
+  </si>
+  <si>
+    <t>03666645600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4755A</t>
+  </si>
+  <si>
+    <t>03668212900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE250D</t>
+  </si>
+  <si>
+    <t>03414844600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF8A6D</t>
+  </si>
+  <si>
+    <t>03416154200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL41797</t>
+  </si>
+  <si>
+    <t>03417353100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL71CE3</t>
+  </si>
+  <si>
+    <t>03418752100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC8E5D</t>
+  </si>
+  <si>
+    <t>03847171700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLEB58C</t>
+  </si>
+  <si>
+    <t>03847931100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL7590B</t>
+  </si>
+  <si>
+    <t>03848410000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLED2A1</t>
+  </si>
+  <si>
+    <t>03848821900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL23AC9</t>
+  </si>
+  <si>
+    <t>03048873600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF7F06</t>
+  </si>
+  <si>
+    <t>03049303400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2C4D2</t>
+  </si>
+  <si>
+    <t>03049739000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDAA23</t>
+  </si>
+  <si>
+    <t>03050276300</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1203,7 @@
     </row>
     <row r="2" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>74</v>
@@ -1086,7 +1230,7 @@
         <v>26.36</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>24.01085412757735</v>
+        <v>24.43591250434271</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>80</v>
@@ -1167,7 +1311,7 @@
         <v>96</v>
       </c>
       <c r="BJ2" s="5" t="s">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="BK2" s="1" t="s">
         <v>97</v>
@@ -1181,7 +1325,7 @@
     </row>
     <row r="3" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>98</v>
@@ -1208,7 +1352,7 @@
         <v>26.36</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>24.139473632188565</v>
+        <v>24.951090911490727</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>80</v>
@@ -1289,7 +1433,7 @@
         <v>96</v>
       </c>
       <c r="BJ3" s="5" t="s">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="BK3" s="1" t="s">
         <v>97</v>
@@ -1303,7 +1447,7 @@
     </row>
     <row r="4" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>99</v>
@@ -1330,7 +1474,7 @@
         <v>26.36</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>24.77904887564629</v>
+        <v>24.55522971073949</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>80</v>
@@ -1411,7 +1555,7 @@
         <v>96</v>
       </c>
       <c r="BJ4" s="5" t="s">
-        <v>132</v>
+        <v>180</v>
       </c>
       <c r="BK4" s="1" t="s">
         <v>97</v>
@@ -1425,7 +1569,7 @@
     </row>
     <row r="5" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>133</v>
+        <v>181</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>100</v>
@@ -1452,7 +1596,7 @@
         <v>26.36</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>24.23184957564713</v>
+        <v>24.787658661416586</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>80</v>
@@ -1533,7 +1677,7 @@
         <v>96</v>
       </c>
       <c r="BJ5" s="5" t="s">
-        <v>134</v>
+        <v>182</v>
       </c>
       <c r="BK5" s="1" t="s">
         <v>97</v>

--- a/ResourcesBD/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesBD/ExcelTemplateForOutletCreation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="199">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -568,6 +568,54 @@
   </si>
   <si>
     <t>03050276300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD07DF</t>
+  </si>
+  <si>
+    <t>03371454000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC46D7</t>
+  </si>
+  <si>
+    <t>03372099900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD57E6</t>
+  </si>
+  <si>
+    <t>03372668100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL91377</t>
+  </si>
+  <si>
+    <t>03373147300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL53A49</t>
+  </si>
+  <si>
+    <t>03629219700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDB73D</t>
+  </si>
+  <si>
+    <t>03629839200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE8F78</t>
+  </si>
+  <si>
+    <t>03630341100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBC979</t>
+  </si>
+  <si>
+    <t>03630794800</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1251,7 @@
     </row>
     <row r="2" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>74</v>
@@ -1230,7 +1278,7 @@
         <v>26.36</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>24.43591250434271</v>
+        <v>24.702193981934734</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>80</v>
@@ -1311,7 +1359,7 @@
         <v>96</v>
       </c>
       <c r="BJ2" s="5" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="BK2" s="1" t="s">
         <v>97</v>
@@ -1325,7 +1373,7 @@
     </row>
     <row r="3" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>98</v>
@@ -1352,7 +1400,7 @@
         <v>26.36</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>24.951090911490727</v>
+        <v>24.264599748748747</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>80</v>
@@ -1433,7 +1481,7 @@
         <v>96</v>
       </c>
       <c r="BJ3" s="5" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="BK3" s="1" t="s">
         <v>97</v>
@@ -1447,7 +1495,7 @@
     </row>
     <row r="4" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>99</v>
@@ -1474,7 +1522,7 @@
         <v>26.36</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>24.55522971073949</v>
+        <v>24.213130370818085</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>80</v>
@@ -1555,7 +1603,7 @@
         <v>96</v>
       </c>
       <c r="BJ4" s="5" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="BK4" s="1" t="s">
         <v>97</v>
@@ -1569,7 +1617,7 @@
     </row>
     <row r="5" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>100</v>
@@ -1596,7 +1644,7 @@
         <v>26.36</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>24.787658661416586</v>
+        <v>24.734087759984497</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>80</v>
@@ -1677,7 +1725,7 @@
         <v>96</v>
       </c>
       <c r="BJ5" s="5" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="BK5" s="1" t="s">
         <v>97</v>

--- a/ResourcesBD/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesBD/ExcelTemplateForOutletCreation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="215">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -616,6 +616,54 @@
   </si>
   <si>
     <t>03630794800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL33E9F</t>
+  </si>
+  <si>
+    <t>03654907400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2D94E</t>
+  </si>
+  <si>
+    <t>03655515200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF3E41</t>
+  </si>
+  <si>
+    <t>03656015400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA9D36</t>
+  </si>
+  <si>
+    <t>03656501400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDC589</t>
+  </si>
+  <si>
+    <t>03979754000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL35075</t>
+  </si>
+  <si>
+    <t>03980335600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9F4F0</t>
+  </si>
+  <si>
+    <t>03980675900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3EF47</t>
+  </si>
+  <si>
+    <t>03980977200</t>
   </si>
 </sst>
 </file>
@@ -1251,7 +1299,7 @@
     </row>
     <row r="2" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>74</v>
@@ -1278,7 +1326,7 @@
         <v>26.36</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>24.702193981934734</v>
+        <v>24.84646300959945</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>80</v>
@@ -1359,7 +1407,7 @@
         <v>96</v>
       </c>
       <c r="BJ2" s="5" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="BK2" s="1" t="s">
         <v>97</v>
@@ -1373,7 +1421,7 @@
     </row>
     <row r="3" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>98</v>
@@ -1400,7 +1448,7 @@
         <v>26.36</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>24.264599748748747</v>
+        <v>24.159674833662173</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>80</v>
@@ -1481,7 +1529,7 @@
         <v>96</v>
       </c>
       <c r="BJ3" s="5" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="BK3" s="1" t="s">
         <v>97</v>
@@ -1495,7 +1543,7 @@
     </row>
     <row r="4" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>99</v>
@@ -1522,7 +1570,7 @@
         <v>26.36</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>24.213130370818085</v>
+        <v>24.317760249146865</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>80</v>
@@ -1603,7 +1651,7 @@
         <v>96</v>
       </c>
       <c r="BJ4" s="5" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="BK4" s="1" t="s">
         <v>97</v>
@@ -1617,7 +1665,7 @@
     </row>
     <row r="5" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>100</v>
@@ -1644,7 +1692,7 @@
         <v>26.36</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>24.734087759984497</v>
+        <v>24.1220566392675</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>80</v>
@@ -1725,7 +1773,7 @@
         <v>96</v>
       </c>
       <c r="BJ5" s="5" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="BK5" s="1" t="s">
         <v>97</v>

--- a/ResourcesBD/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesBD/ExcelTemplateForOutletCreation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="335">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -664,6 +664,366 @@
   </si>
   <si>
     <t>03980977200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDFB22</t>
+  </si>
+  <si>
+    <t>03885142200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC0EB8</t>
+  </si>
+  <si>
+    <t>03885925500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5364B</t>
+  </si>
+  <si>
+    <t>03886474500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL75356</t>
+  </si>
+  <si>
+    <t>03887086200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL63E4E</t>
+  </si>
+  <si>
+    <t>03629603500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLEDECB</t>
+  </si>
+  <si>
+    <t>03630302900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL869D3</t>
+  </si>
+  <si>
+    <t>03630885600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6CAF4</t>
+  </si>
+  <si>
+    <t>03631406600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4FDED</t>
+  </si>
+  <si>
+    <t>03083815300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC976C</t>
+  </si>
+  <si>
+    <t>03085330100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL863E9</t>
+  </si>
+  <si>
+    <t>03086355000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC76EE</t>
+  </si>
+  <si>
+    <t>03087254700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF9C0F</t>
+  </si>
+  <si>
+    <t>03241908100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL36848</t>
+  </si>
+  <si>
+    <t>03243402000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL7744F</t>
+  </si>
+  <si>
+    <t>03244487500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL95D93</t>
+  </si>
+  <si>
+    <t>03245694100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBE0C6</t>
+  </si>
+  <si>
+    <t>03345728700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8E3AE</t>
+  </si>
+  <si>
+    <t>03347281700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL92C9B</t>
+  </si>
+  <si>
+    <t>03348403100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL87C9C</t>
+  </si>
+  <si>
+    <t>03349418200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2D348</t>
+  </si>
+  <si>
+    <t>03780313400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL60212</t>
+  </si>
+  <si>
+    <t>03781943500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL05A4E</t>
+  </si>
+  <si>
+    <t>03783731700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF39A2</t>
+  </si>
+  <si>
+    <t>03785274700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL46C75</t>
+  </si>
+  <si>
+    <t>03363436900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB1894</t>
+  </si>
+  <si>
+    <t>03364826300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE4512</t>
+  </si>
+  <si>
+    <t>03365780200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL26F2F</t>
+  </si>
+  <si>
+    <t>03366778100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL85826</t>
+  </si>
+  <si>
+    <t>03376889500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF3EB0</t>
+  </si>
+  <si>
+    <t>03377781100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE61CD</t>
+  </si>
+  <si>
+    <t>03378544500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDB853</t>
+  </si>
+  <si>
+    <t>03379255000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL88820</t>
+  </si>
+  <si>
+    <t>03128720000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5A233</t>
+  </si>
+  <si>
+    <t>03130136900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3B6C0</t>
+  </si>
+  <si>
+    <t>03131193500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLAC77B</t>
+  </si>
+  <si>
+    <t>03132451800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA1294</t>
+  </si>
+  <si>
+    <t>03466036600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL007C4</t>
+  </si>
+  <si>
+    <t>03467546900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL33EFE</t>
+  </si>
+  <si>
+    <t>03468681500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3CFDC</t>
+  </si>
+  <si>
+    <t>03469679800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5A547</t>
+  </si>
+  <si>
+    <t>03490733900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL48F36</t>
+  </si>
+  <si>
+    <t>03491207000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD98C7</t>
+  </si>
+  <si>
+    <t>03491615400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL24664</t>
+  </si>
+  <si>
+    <t>03491958700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF2236</t>
+  </si>
+  <si>
+    <t>03407763700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL07E57</t>
+  </si>
+  <si>
+    <t>03408819800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4C34F</t>
+  </si>
+  <si>
+    <t>03409623100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA19EA</t>
+  </si>
+  <si>
+    <t>03410418800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE69DF</t>
+  </si>
+  <si>
+    <t>03954672300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL20346</t>
+  </si>
+  <si>
+    <t>03955191300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL786EA</t>
+  </si>
+  <si>
+    <t>03955556900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL372CF</t>
+  </si>
+  <si>
+    <t>03955873200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL06003</t>
+  </si>
+  <si>
+    <t>03469757900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA858E</t>
+  </si>
+  <si>
+    <t>03470212500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5BBC7</t>
+  </si>
+  <si>
+    <t>03470683700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL21F5A</t>
+  </si>
+  <si>
+    <t>03471113700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6F3B3</t>
+  </si>
+  <si>
+    <t>03069210000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA5556</t>
+  </si>
+  <si>
+    <t>03070041200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL585BF</t>
+  </si>
+  <si>
+    <t>03070794300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL13721</t>
+  </si>
+  <si>
+    <t>03071301300</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1659,7 @@
     </row>
     <row r="2" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>207</v>
+        <v>327</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>74</v>
@@ -1326,7 +1686,7 @@
         <v>26.36</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>24.84646300959945</v>
+        <v>24.878051902407005</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>80</v>
@@ -1407,7 +1767,7 @@
         <v>96</v>
       </c>
       <c r="BJ2" s="5" t="s">
-        <v>208</v>
+        <v>328</v>
       </c>
       <c r="BK2" s="1" t="s">
         <v>97</v>
@@ -1421,7 +1781,7 @@
     </row>
     <row r="3" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>209</v>
+        <v>329</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>98</v>
@@ -1448,7 +1808,7 @@
         <v>26.36</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>24.159674833662173</v>
+        <v>24.664902173231344</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>80</v>
@@ -1529,7 +1889,7 @@
         <v>96</v>
       </c>
       <c r="BJ3" s="5" t="s">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="BK3" s="1" t="s">
         <v>97</v>
@@ -1543,7 +1903,7 @@
     </row>
     <row r="4" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>211</v>
+        <v>331</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>99</v>
@@ -1570,7 +1930,7 @@
         <v>26.36</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>24.317760249146865</v>
+        <v>24.980497247428474</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>80</v>
@@ -1651,7 +2011,7 @@
         <v>96</v>
       </c>
       <c r="BJ4" s="5" t="s">
-        <v>212</v>
+        <v>332</v>
       </c>
       <c r="BK4" s="1" t="s">
         <v>97</v>
@@ -1665,7 +2025,7 @@
     </row>
     <row r="5" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>213</v>
+        <v>333</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>100</v>
@@ -1692,7 +2052,7 @@
         <v>26.36</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>24.1220566392675</v>
+        <v>24.11215040762057</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>80</v>
@@ -1773,7 +2133,7 @@
         <v>96</v>
       </c>
       <c r="BJ5" s="5" t="s">
-        <v>214</v>
+        <v>334</v>
       </c>
       <c r="BK5" s="1" t="s">
         <v>97</v>

--- a/ResourcesBD/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesBD/ExcelTemplateForOutletCreation.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Excel Template" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" concurrentManualCount="8"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="122">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -321,709 +321,70 @@
     <t>Hammad Outlet18</t>
   </si>
   <si>
-    <t>Hammad Outlet19</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL65444</t>
-  </si>
-  <si>
-    <t>03409419300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC0EFD</t>
-  </si>
-  <si>
-    <t>03410887200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLEA06B</t>
-  </si>
-  <si>
-    <t>03411859600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLABA79</t>
-  </si>
-  <si>
-    <t>03414399000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00001 </t>
-  </si>
-  <si>
     <t>00001</t>
   </si>
   <si>
-    <t>AUTO_OUTLD054F</t>
-  </si>
-  <si>
-    <t>03178270500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE2358</t>
-  </si>
-  <si>
-    <t>03179270600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL5FD38</t>
-  </si>
-  <si>
-    <t>03180106700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC61CF</t>
-  </si>
-  <si>
-    <t>03180933600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL1F7B8</t>
-  </si>
-  <si>
-    <t>03300124100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLCC4FE</t>
-  </si>
-  <si>
-    <t>03301238800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF1F08</t>
-  </si>
-  <si>
-    <t>03302260600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLEE7E8</t>
-  </si>
-  <si>
-    <t>03303520000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL0A15A</t>
-  </si>
-  <si>
-    <t>03223040600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE0108</t>
-  </si>
-  <si>
-    <t>03225272900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL4B7D4</t>
-  </si>
-  <si>
-    <t>03226759800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL60D83</t>
-  </si>
-  <si>
-    <t>03228174400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL249EC</t>
-  </si>
-  <si>
-    <t>03539130700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLA2B6E</t>
-  </si>
-  <si>
-    <t>03540558600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL7CE9F</t>
-  </si>
-  <si>
-    <t>03541597700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL59EC1</t>
-  </si>
-  <si>
-    <t>03542875200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLA9C3D</t>
-  </si>
-  <si>
-    <t>03909766800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL96B93</t>
-  </si>
-  <si>
-    <t>03911744600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL4E430</t>
-  </si>
-  <si>
-    <t>03913291900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLB6B16</t>
-  </si>
-  <si>
-    <t>03915102400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3DE0B</t>
-  </si>
-  <si>
-    <t>03662644600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL5C07A</t>
-  </si>
-  <si>
-    <t>03664407300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL25C26</t>
-  </si>
-  <si>
-    <t>03666645600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL4755A</t>
-  </si>
-  <si>
-    <t>03668212900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE250D</t>
-  </si>
-  <si>
-    <t>03414844600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF8A6D</t>
-  </si>
-  <si>
-    <t>03416154200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL41797</t>
-  </si>
-  <si>
-    <t>03417353100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL71CE3</t>
-  </si>
-  <si>
-    <t>03418752100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC8E5D</t>
-  </si>
-  <si>
-    <t>03847171700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLEB58C</t>
-  </si>
-  <si>
-    <t>03847931100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL7590B</t>
-  </si>
-  <si>
-    <t>03848410000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLED2A1</t>
-  </si>
-  <si>
-    <t>03848821900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL23AC9</t>
-  </si>
-  <si>
-    <t>03048873600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF7F06</t>
-  </si>
-  <si>
-    <t>03049303400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2C4D2</t>
-  </si>
-  <si>
-    <t>03049739000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLDAA23</t>
-  </si>
-  <si>
-    <t>03050276300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD07DF</t>
-  </si>
-  <si>
-    <t>03371454000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC46D7</t>
-  </si>
-  <si>
-    <t>03372099900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD57E6</t>
-  </si>
-  <si>
-    <t>03372668100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL91377</t>
-  </si>
-  <si>
-    <t>03373147300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL53A49</t>
-  </si>
-  <si>
-    <t>03629219700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLDB73D</t>
-  </si>
-  <si>
-    <t>03629839200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE8F78</t>
-  </si>
-  <si>
-    <t>03630341100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLBC979</t>
-  </si>
-  <si>
-    <t>03630794800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL33E9F</t>
-  </si>
-  <si>
-    <t>03654907400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2D94E</t>
-  </si>
-  <si>
-    <t>03655515200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF3E41</t>
-  </si>
-  <si>
-    <t>03656015400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLA9D36</t>
-  </si>
-  <si>
-    <t>03656501400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLDC589</t>
-  </si>
-  <si>
-    <t>03979754000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL35075</t>
-  </si>
-  <si>
-    <t>03980335600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL9F4F0</t>
-  </si>
-  <si>
-    <t>03980675900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3EF47</t>
-  </si>
-  <si>
-    <t>03980977200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLDFB22</t>
-  </si>
-  <si>
-    <t>03885142200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC0EB8</t>
-  </si>
-  <si>
-    <t>03885925500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL5364B</t>
-  </si>
-  <si>
-    <t>03886474500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL75356</t>
-  </si>
-  <si>
-    <t>03887086200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL63E4E</t>
-  </si>
-  <si>
-    <t>03629603500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLEDECB</t>
-  </si>
-  <si>
-    <t>03630302900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL869D3</t>
-  </si>
-  <si>
-    <t>03630885600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL6CAF4</t>
-  </si>
-  <si>
-    <t>03631406600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL4FDED</t>
-  </si>
-  <si>
-    <t>03083815300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC976C</t>
-  </si>
-  <si>
-    <t>03085330100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL863E9</t>
-  </si>
-  <si>
-    <t>03086355000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC76EE</t>
-  </si>
-  <si>
-    <t>03087254700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF9C0F</t>
-  </si>
-  <si>
-    <t>03241908100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL36848</t>
-  </si>
-  <si>
-    <t>03243402000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL7744F</t>
-  </si>
-  <si>
-    <t>03244487500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL95D93</t>
-  </si>
-  <si>
-    <t>03245694100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLBE0C6</t>
-  </si>
-  <si>
-    <t>03345728700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL8E3AE</t>
-  </si>
-  <si>
-    <t>03347281700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL92C9B</t>
-  </si>
-  <si>
-    <t>03348403100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL87C9C</t>
-  </si>
-  <si>
-    <t>03349418200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2D348</t>
-  </si>
-  <si>
-    <t>03780313400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL60212</t>
-  </si>
-  <si>
-    <t>03781943500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL05A4E</t>
-  </si>
-  <si>
-    <t>03783731700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF39A2</t>
-  </si>
-  <si>
-    <t>03785274700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL46C75</t>
-  </si>
-  <si>
-    <t>03363436900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLB1894</t>
-  </si>
-  <si>
-    <t>03364826300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE4512</t>
-  </si>
-  <si>
-    <t>03365780200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL26F2F</t>
-  </si>
-  <si>
-    <t>03366778100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL85826</t>
-  </si>
-  <si>
-    <t>03376889500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF3EB0</t>
-  </si>
-  <si>
-    <t>03377781100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE61CD</t>
-  </si>
-  <si>
-    <t>03378544500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLDB853</t>
-  </si>
-  <si>
-    <t>03379255000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL88820</t>
-  </si>
-  <si>
-    <t>03128720000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL5A233</t>
-  </si>
-  <si>
-    <t>03130136900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3B6C0</t>
-  </si>
-  <si>
-    <t>03131193500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLAC77B</t>
-  </si>
-  <si>
-    <t>03132451800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLA1294</t>
-  </si>
-  <si>
-    <t>03466036600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL007C4</t>
-  </si>
-  <si>
-    <t>03467546900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL33EFE</t>
-  </si>
-  <si>
-    <t>03468681500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3CFDC</t>
-  </si>
-  <si>
-    <t>03469679800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL5A547</t>
-  </si>
-  <si>
-    <t>03490733900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL48F36</t>
-  </si>
-  <si>
-    <t>03491207000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD98C7</t>
-  </si>
-  <si>
-    <t>03491615400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL24664</t>
-  </si>
-  <si>
-    <t>03491958700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF2236</t>
-  </si>
-  <si>
-    <t>03407763700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL07E57</t>
-  </si>
-  <si>
-    <t>03408819800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL4C34F</t>
-  </si>
-  <si>
-    <t>03409623100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLA19EA</t>
-  </si>
-  <si>
-    <t>03410418800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE69DF</t>
-  </si>
-  <si>
-    <t>03954672300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL20346</t>
-  </si>
-  <si>
-    <t>03955191300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL786EA</t>
-  </si>
-  <si>
-    <t>03955556900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL372CF</t>
-  </si>
-  <si>
-    <t>03955873200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL06003</t>
-  </si>
-  <si>
-    <t>03469757900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLA858E</t>
-  </si>
-  <si>
-    <t>03470212500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL5BBC7</t>
-  </si>
-  <si>
-    <t>03470683700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL21F5A</t>
-  </si>
-  <si>
-    <t>03471113700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL6F3B3</t>
-  </si>
-  <si>
-    <t>03069210000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLA5556</t>
-  </si>
-  <si>
-    <t>03070041200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL585BF</t>
-  </si>
-  <si>
-    <t>03070794300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL13721</t>
-  </si>
-  <si>
-    <t>03071301300</t>
+    <t>AUTO_OUTLA88C8</t>
+  </si>
+  <si>
+    <t>03972648500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF324B</t>
+  </si>
+  <si>
+    <t>03973655000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4FD95</t>
+  </si>
+  <si>
+    <t>03974281300</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3C102</t>
+  </si>
+  <si>
+    <t>03394468400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL66E57</t>
+  </si>
+  <si>
+    <t>03395387100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9917B</t>
+  </si>
+  <si>
+    <t>03395959800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3423B</t>
+  </si>
+  <si>
+    <t>03419093300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA7C32</t>
+  </si>
+  <si>
+    <t>03420264500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2BAE2</t>
+  </si>
+  <si>
+    <t>03421117000</t>
   </si>
 </sst>
 </file>
@@ -1067,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1075,6 +436,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1355,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BV5"/>
+  <dimension ref="A1:BV4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="10.7265625"/>
@@ -1659,7 +1021,7 @@
     </row>
     <row r="2" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>327</v>
+        <v>116</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>74</v>
@@ -1686,7 +1048,7 @@
         <v>26.36</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>24.878051902407005</v>
+        <v>24.665149954259327</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>80</v>
@@ -1709,6 +1071,9 @@
       <c r="AA2" t="s" s="0">
         <v>84</v>
       </c>
+      <c r="AB2" t="s" s="0">
+        <v>83</v>
+      </c>
       <c r="AC2" t="s" s="0">
         <v>85</v>
       </c>
@@ -1718,6 +1083,9 @@
       <c r="AH2" t="s" s="0">
         <v>84</v>
       </c>
+      <c r="AN2" s="7" t="s">
+        <v>83</v>
+      </c>
       <c r="AP2" s="1" t="s">
         <v>86</v>
       </c>
@@ -1734,7 +1102,7 @@
         <v>90</v>
       </c>
       <c r="AU2" s="5" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="AV2" s="1" t="s">
         <v>91</v>
@@ -1767,10 +1135,16 @@
         <v>96</v>
       </c>
       <c r="BJ2" s="5" t="s">
-        <v>328</v>
+        <v>117</v>
       </c>
       <c r="BK2" s="1" t="s">
         <v>97</v>
+      </c>
+      <c r="BM2" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="BO2" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="BU2" s="1" t="s">
         <v>94</v>
@@ -1781,7 +1155,7 @@
     </row>
     <row r="3" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>329</v>
+        <v>118</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>98</v>
@@ -1808,7 +1182,7 @@
         <v>26.36</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>24.664902173231344</v>
+        <v>24.30760405319391</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>80</v>
@@ -1831,6 +1205,9 @@
       <c r="AA3" t="s" s="0">
         <v>84</v>
       </c>
+      <c r="AB3" t="s" s="0">
+        <v>83</v>
+      </c>
       <c r="AC3" t="s" s="0">
         <v>85</v>
       </c>
@@ -1840,6 +1217,9 @@
       <c r="AH3" t="s" s="0">
         <v>84</v>
       </c>
+      <c r="AN3" s="7" t="s">
+        <v>83</v>
+      </c>
       <c r="AP3" s="1" t="s">
         <v>86</v>
       </c>
@@ -1856,7 +1236,7 @@
         <v>90</v>
       </c>
       <c r="AU3" s="5" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="AV3" s="1" t="s">
         <v>91</v>
@@ -1889,10 +1269,16 @@
         <v>96</v>
       </c>
       <c r="BJ3" s="5" t="s">
-        <v>330</v>
+        <v>119</v>
       </c>
       <c r="BK3" s="1" t="s">
         <v>97</v>
+      </c>
+      <c r="BM3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="BO3" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="BU3" s="1" t="s">
         <v>94</v>
@@ -1903,7 +1289,7 @@
     </row>
     <row r="4" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>331</v>
+        <v>120</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>99</v>
@@ -1930,7 +1316,7 @@
         <v>26.36</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>24.980497247428474</v>
+        <v>24.40725232912449</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>80</v>
@@ -1953,6 +1339,9 @@
       <c r="AA4" t="s" s="0">
         <v>84</v>
       </c>
+      <c r="AB4" t="s" s="0">
+        <v>83</v>
+      </c>
       <c r="AC4" t="s" s="0">
         <v>85</v>
       </c>
@@ -1962,6 +1351,9 @@
       <c r="AH4" t="s" s="0">
         <v>84</v>
       </c>
+      <c r="AN4" s="7" t="s">
+        <v>83</v>
+      </c>
       <c r="AP4" s="1" t="s">
         <v>86</v>
       </c>
@@ -1978,7 +1370,7 @@
         <v>90</v>
       </c>
       <c r="AU4" s="5" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AV4" s="1" t="s">
         <v>91</v>
@@ -2011,137 +1403,21 @@
         <v>96</v>
       </c>
       <c r="BJ4" s="5" t="s">
-        <v>332</v>
+        <v>121</v>
       </c>
       <c r="BK4" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="BM4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="BO4" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="BU4" s="1" t="s">
         <v>94</v>
       </c>
       <c r="BV4" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:74" x14ac:dyDescent="0.35">
-      <c r="B5" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O5" s="3">
-        <v>26.36</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>24.11215040762057</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="T5" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="U5" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="X5" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y5" t="s" s="0">
-        <v>83</v>
-      </c>
-      <c r="Z5" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="AA5" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="AC5" t="s" s="0">
-        <v>85</v>
-      </c>
-      <c r="AD5" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="AH5" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="AP5" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AQ5" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AS5" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AT5" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AU5" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="AV5" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AW5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY5" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AZ5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="BA5" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC5" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="BD5" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="BE5" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="BF5" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BG5" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="BJ5" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="BK5" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="BU5" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="BV5" s="1" t="s">
         <v>94</v>
       </c>
     </row>

--- a/ResourcesBD/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesBD/ExcelTemplateForOutletCreation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="134">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -385,6 +385,42 @@
   </si>
   <si>
     <t>03421117000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL7482C</t>
+  </si>
+  <si>
+    <t>03890292700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8B219</t>
+  </si>
+  <si>
+    <t>03891624400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1B01A</t>
+  </si>
+  <si>
+    <t>03892577300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8E8A8</t>
+  </si>
+  <si>
+    <t>03931565500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL64BC0</t>
+  </si>
+  <si>
+    <t>03933017300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1CB6E</t>
+  </si>
+  <si>
+    <t>03933929400</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1057,7 @@
     </row>
     <row r="2" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>74</v>
@@ -1048,7 +1084,7 @@
         <v>26.36</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>24.665149954259327</v>
+        <v>24.821569101212024</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>80</v>
@@ -1135,7 +1171,7 @@
         <v>96</v>
       </c>
       <c r="BJ2" s="5" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="BK2" s="1" t="s">
         <v>97</v>
@@ -1155,7 +1191,7 @@
     </row>
     <row r="3" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>98</v>
@@ -1182,7 +1218,7 @@
         <v>26.36</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>24.30760405319391</v>
+        <v>24.60360144272134</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>80</v>
@@ -1269,7 +1305,7 @@
         <v>96</v>
       </c>
       <c r="BJ3" s="5" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="BK3" s="1" t="s">
         <v>97</v>
@@ -1289,7 +1325,7 @@
     </row>
     <row r="4" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>99</v>
@@ -1316,7 +1352,7 @@
         <v>26.36</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>24.40725232912449</v>
+        <v>24.557970319329627</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>80</v>
@@ -1403,7 +1439,7 @@
         <v>96</v>
       </c>
       <c r="BJ4" s="5" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="BK4" s="1" t="s">
         <v>97</v>

--- a/ResourcesBD/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesBD/ExcelTemplateForOutletCreation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="278">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -258,9 +258,6 @@
     <t>C01047</t>
   </si>
   <si>
-    <t>002001D05033D10611D33063D95869</t>
-  </si>
-  <si>
     <t>01</t>
   </si>
   <si>
@@ -324,24 +321,6 @@
     <t>00001</t>
   </si>
   <si>
-    <t>AUTO_OUTLA88C8</t>
-  </si>
-  <si>
-    <t>03972648500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF324B</t>
-  </si>
-  <si>
-    <t>03973655000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL4FD95</t>
-  </si>
-  <si>
-    <t>03974281300</t>
-  </si>
-  <si>
     <t>123</t>
   </si>
   <si>
@@ -351,76 +330,529 @@
     <t>125</t>
   </si>
   <si>
-    <t>AUTO_OUTL3C102</t>
-  </si>
-  <si>
-    <t>03394468400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL66E57</t>
-  </si>
-  <si>
-    <t>03395387100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL9917B</t>
-  </si>
-  <si>
-    <t>03395959800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3423B</t>
-  </si>
-  <si>
-    <t>03419093300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLA7C32</t>
-  </si>
-  <si>
-    <t>03420264500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2BAE2</t>
-  </si>
-  <si>
-    <t>03421117000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL7482C</t>
-  </si>
-  <si>
-    <t>03890292700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL8B219</t>
-  </si>
-  <si>
-    <t>03891624400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL1B01A</t>
-  </si>
-  <si>
-    <t>03892577300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL8E8A8</t>
-  </si>
-  <si>
-    <t>03931565500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL64BC0</t>
-  </si>
-  <si>
-    <t>03933017300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL1CB6E</t>
-  </si>
-  <si>
-    <t>03933929400</t>
+    <t>AUTO_OUTLAEA5A</t>
+  </si>
+  <si>
+    <t>03272157900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8C0B2</t>
+  </si>
+  <si>
+    <t>03273619600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0F974</t>
+  </si>
+  <si>
+    <t>03274711500</t>
+  </si>
+  <si>
+    <t>002001D01224D10796D33059D95890</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL635B2</t>
+  </si>
+  <si>
+    <t>03734530100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL43531</t>
+  </si>
+  <si>
+    <t>03735678400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL53ADC</t>
+  </si>
+  <si>
+    <t>03736387700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6B8DC</t>
+  </si>
+  <si>
+    <t>03755034600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0CFD3</t>
+  </si>
+  <si>
+    <t>03755885200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL53B97</t>
+  </si>
+  <si>
+    <t>03756541200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4B187</t>
+  </si>
+  <si>
+    <t>03103651700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL35951</t>
+  </si>
+  <si>
+    <t>03104641400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL45BFB</t>
+  </si>
+  <si>
+    <t>03105411700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL77252</t>
+  </si>
+  <si>
+    <t>03947232600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF804D</t>
+  </si>
+  <si>
+    <t>03948146400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3E870</t>
+  </si>
+  <si>
+    <t>03948637700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5A2AF</t>
+  </si>
+  <si>
+    <t>03841404800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF2169</t>
+  </si>
+  <si>
+    <t>03842694600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL93B19</t>
+  </si>
+  <si>
+    <t>03843534700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL72751</t>
+  </si>
+  <si>
+    <t>03816962900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2F15C</t>
+  </si>
+  <si>
+    <t>03817530200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL22D07</t>
+  </si>
+  <si>
+    <t>03818236000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5A10D</t>
+  </si>
+  <si>
+    <t>03804329800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA605A</t>
+  </si>
+  <si>
+    <t>03805295200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9FCA8</t>
+  </si>
+  <si>
+    <t>03806134600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5BD53</t>
+  </si>
+  <si>
+    <t>03894300800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC8A5B</t>
+  </si>
+  <si>
+    <t>03895317500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL398A6</t>
+  </si>
+  <si>
+    <t>03896048200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC40EB</t>
+  </si>
+  <si>
+    <t>03885862000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD567C</t>
+  </si>
+  <si>
+    <t>03887000400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6676F</t>
+  </si>
+  <si>
+    <t>03887915200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLEAA54</t>
+  </si>
+  <si>
+    <t>03764854900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4B909</t>
+  </si>
+  <si>
+    <t>03765760700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA42D7</t>
+  </si>
+  <si>
+    <t>03766213600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL04652</t>
+  </si>
+  <si>
+    <t>03183053100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL44E56</t>
+  </si>
+  <si>
+    <t>03183589400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF533E</t>
+  </si>
+  <si>
+    <t>03184026600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF38BC</t>
+  </si>
+  <si>
+    <t>03114205300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL69134</t>
+  </si>
+  <si>
+    <t>03115174100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9821C</t>
+  </si>
+  <si>
+    <t>03115878600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF4CD0</t>
+  </si>
+  <si>
+    <t>03392469400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL55F40</t>
+  </si>
+  <si>
+    <t>03394459400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL25842</t>
+  </si>
+  <si>
+    <t>03395957400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB3842</t>
+  </si>
+  <si>
+    <t>03228320500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL96C74</t>
+  </si>
+  <si>
+    <t>03230159600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD2E03</t>
+  </si>
+  <si>
+    <t>03231955700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD815B</t>
+  </si>
+  <si>
+    <t>03868652100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE998F</t>
+  </si>
+  <si>
+    <t>03871218600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD837C</t>
+  </si>
+  <si>
+    <t>03872935300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL137A9</t>
+  </si>
+  <si>
+    <t>03998067400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0D010</t>
+  </si>
+  <si>
+    <t>03998645800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD1CDB</t>
+  </si>
+  <si>
+    <t>03999224100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCF0F8</t>
+  </si>
+  <si>
+    <t>03273687900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1D9D4</t>
+  </si>
+  <si>
+    <t>03274306800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBFAD5</t>
+  </si>
+  <si>
+    <t>03274776400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL212B4</t>
+  </si>
+  <si>
+    <t>03311834100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3C901</t>
+  </si>
+  <si>
+    <t>03313678200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE49A1</t>
+  </si>
+  <si>
+    <t>03315109100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1085C</t>
+  </si>
+  <si>
+    <t>03023245000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL02F11</t>
+  </si>
+  <si>
+    <t>03024905600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL14F31</t>
+  </si>
+  <si>
+    <t>03026255000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLECBD6</t>
+  </si>
+  <si>
+    <t>03234259100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDF92B</t>
+  </si>
+  <si>
+    <t>03236200100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC9053</t>
+  </si>
+  <si>
+    <t>03237336000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL26CD7</t>
+  </si>
+  <si>
+    <t>03340935100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC12CF</t>
+  </si>
+  <si>
+    <t>03345719200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLAE8EB</t>
+  </si>
+  <si>
+    <t>03348209300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL57CF5</t>
+  </si>
+  <si>
+    <t>03174856500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD3C5D</t>
+  </si>
+  <si>
+    <t>03176170300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL19535</t>
+  </si>
+  <si>
+    <t>03177131700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0207C</t>
+  </si>
+  <si>
+    <t>03711345600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC779B</t>
+  </si>
+  <si>
+    <t>03712609900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL66F9A</t>
+  </si>
+  <si>
+    <t>03713776500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL056FE</t>
+  </si>
+  <si>
+    <t>03933096500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB5DB6</t>
+  </si>
+  <si>
+    <t>03934195600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD006F</t>
+  </si>
+  <si>
+    <t>03935149100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL03ABE</t>
+  </si>
+  <si>
+    <t>03548111300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL46D86</t>
+  </si>
+  <si>
+    <t>03548857400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL00A98</t>
+  </si>
+  <si>
+    <t>03549401300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL90EBA</t>
+  </si>
+  <si>
+    <t>03256989300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE29C7</t>
+  </si>
+  <si>
+    <t>03257611700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE279C</t>
+  </si>
+  <si>
+    <t>03258327500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLAA386</t>
+  </si>
+  <si>
+    <t>03963237600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL504C9</t>
+  </si>
+  <si>
+    <t>03964696700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF63BE</t>
+  </si>
+  <si>
+    <t>03965499500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL66B04</t>
+  </si>
+  <si>
+    <t>03100313500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE1B9D</t>
+  </si>
+  <si>
+    <t>03101067800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA5627</t>
+  </si>
+  <si>
+    <t>03101725300</t>
   </si>
 </sst>
 </file>
@@ -769,7 +1201,7 @@
     <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="18.26953125"/>
     <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="11.6328125"/>
     <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.26953125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="18.54296875"/>
+    <col min="14" max="14" customWidth="true" style="1" width="42.26953125"/>
     <col min="15" max="15" bestFit="true" customWidth="true" style="3" width="10.0"/>
     <col min="16" max="16" bestFit="true" customWidth="true" style="3" width="8.54296875"/>
     <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="10.453125"/>
@@ -1057,7 +1489,7 @@
     </row>
     <row r="2" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>128</v>
+        <v>272</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>74</v>
@@ -1077,127 +1509,127 @@
       <c r="M2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>79</v>
+      <c r="N2" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="O2" s="3">
         <v>26.36</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>24.821569101212024</v>
+        <v>24.603401011952744</v>
       </c>
       <c r="S2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T2" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="U2" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="X2" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y2" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="Z2" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="AA2" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="AB2" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="Y2" t="s" s="0">
+      <c r="AC2" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="AD2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="Z2" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="AA2" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AH2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="AC2" t="s" s="0">
+      <c r="AN2" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AD2" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="AH2" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="AN2" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AU2" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AV2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="AU2" s="5" t="s">
+      <c r="AW2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AZ2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="BA2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="BD2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="BE2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="BF2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BG2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="BJ2" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="BK2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BM2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AV2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AW2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AZ2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="BA2" s="1" t="s">
+      <c r="BO2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="BU2" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="BC2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="BD2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="BE2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="BF2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BG2" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="BJ2" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="BK2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="BM2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="BU2" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="BV2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>130</v>
+        <v>274</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>75</v>
@@ -1211,127 +1643,127 @@
       <c r="M3" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>79</v>
+      <c r="N3" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="O3" s="3">
         <v>26.36</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>24.60360144272134</v>
+        <v>24.35610226967044</v>
       </c>
       <c r="S3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T3" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="U3" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="X3" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y3" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="Z3" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="AA3" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="AB3" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="Y3" t="s" s="0">
+      <c r="AC3" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="AD3" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="Z3" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="AA3" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="AB3" t="s" s="0">
+      <c r="AH3" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="AC3" t="s" s="0">
+      <c r="AN3" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP3" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AD3" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="AH3" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="AN3" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="AP3" s="1" t="s">
+      <c r="AQ3" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AQ3" s="1" t="s">
+      <c r="AR3" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="AR3" s="1" t="s">
+      <c r="AS3" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="AS3" s="1" t="s">
+      <c r="AT3" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AT3" s="1" t="s">
+      <c r="AU3" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AV3" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="AU3" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="AV3" s="1" t="s">
+      <c r="AW3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AW3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY3" s="1" t="s">
+      <c r="AZ3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="BA3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="AZ3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="BA3" s="1" t="s">
+      <c r="BC3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="BC3" s="1" t="s">
+      <c r="BD3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="BE3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="BF3" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="BD3" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="BE3" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="BF3" s="1" t="s">
+      <c r="BG3" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="BG3" s="1" t="s">
+      <c r="BJ3" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="BK3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="BJ3" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="BK3" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="BM3" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="BO3" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="BU3" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="BV3" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:74" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>132</v>
+        <v>276</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>75</v>
@@ -1345,116 +1777,116 @@
       <c r="M4" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>79</v>
+      <c r="N4" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="O4" s="3">
         <v>26.36</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>24.557970319329627</v>
+        <v>24.111112814686074</v>
       </c>
       <c r="S4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T4" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="T4" s="5" t="s">
+      <c r="U4" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="X4" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y4" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="Z4" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="AA4" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="AB4" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="Y4" t="s" s="0">
+      <c r="AC4" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="AD4" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="Z4" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="AA4" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="AB4" t="s" s="0">
+      <c r="AH4" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="AC4" t="s" s="0">
+      <c r="AN4" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AD4" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="AH4" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="AN4" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="AP4" s="1" t="s">
+      <c r="AQ4" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AQ4" s="1" t="s">
+      <c r="AR4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="AR4" s="1" t="s">
+      <c r="AS4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="AS4" s="1" t="s">
+      <c r="AT4" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AT4" s="1" t="s">
+      <c r="AU4" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AV4" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="AU4" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="AV4" s="1" t="s">
+      <c r="AW4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY4" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AW4" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY4" s="1" t="s">
+      <c r="AZ4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="BA4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="AZ4" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="BA4" s="1" t="s">
+      <c r="BC4" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="BC4" s="1" t="s">
+      <c r="BD4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="BE4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="BF4" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="BD4" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="BE4" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="BF4" s="1" t="s">
+      <c r="BG4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="BG4" s="1" t="s">
+      <c r="BJ4" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="BK4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="BJ4" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="BK4" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="BM4" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="BO4" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="BU4" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="BV4" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
